--- a/全局定位模块材料清单.xlsx
+++ b/全局定位模块材料清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STM32\code\ops-9\ops9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32541\Desktop\ops9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0016B889-1F23-4CBB-88B0-51D6E1C637E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C121EA-D030-457B-8BB8-FA7520B15AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>序号</t>
   </si>
@@ -234,8 +234,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.4线径，可以换0.5或者0.3
-客服备注：0.4*6*15</t>
+    <t>https://item.taobao.com/item.htm?id=965743472192&amp;mi_id=0000XPuwK9aJ63iKQ_GIob4IwbnGSTuxu6kplt64hiG67Mw&amp;spm=a21xtw.29978518.0.0&amp;xxc=shop&amp;skuId=5438154337255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+铝柱M3*35亮银本色
+群友推荐铝柱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -622,18 +627,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C01B78-34B2-0648-AE77-5B33DEDB2A08}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9.34765625" defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.34765625" style="1"/>
-    <col min="2" max="2" width="15.09765625" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9.34765625" style="1"/>
-    <col min="6" max="6" width="33.8984375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="34.546875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.34765625" style="1"/>
+    <col min="1" max="1" width="9.33203125" style="1"/>
+    <col min="2" max="2" width="15.109375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="9.33203125" style="1"/>
+    <col min="6" max="6" width="33.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -644,7 +651,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -685,7 +692,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -709,7 +716,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="98.7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -733,7 +740,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="84.6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -757,7 +764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="84.6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -780,8 +787,14 @@
       <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+      <c r="H7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -805,7 +818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="84.6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -829,7 +842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="98.7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -853,7 +866,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -877,7 +890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:9" ht="69" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -901,7 +914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -925,7 +938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="69" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -949,7 +962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="84.6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -969,11 +982,8 @@
       <c r="F15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="84.6" x14ac:dyDescent="0.5">
+    </row>
+    <row r="16" spans="1:9" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -997,7 +1007,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1021,7 +1031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
@@ -1032,7 +1042,7 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" ht="70.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -1056,7 +1066,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="98.7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -1080,7 +1090,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E21" s="1">
         <f>SUM(E3:E16)+SUM(E19:E20)</f>
         <v>760.49000000000024</v>
@@ -1109,6 +1119,7 @@
     <hyperlink ref="F17" r:id="rId14" xr:uid="{3E6BB314-3193-469D-8FAD-CD767669AF22}"/>
     <hyperlink ref="F19" r:id="rId15" xr:uid="{D4E5BEFB-FA7B-402D-B0BE-ED67BCCECF55}"/>
     <hyperlink ref="F20" r:id="rId16" xr:uid="{93451804-2F3E-45DF-AA86-BF2DCD758071}"/>
+    <hyperlink ref="H7" r:id="rId17" xr:uid="{3873FF2C-159D-42CC-88E9-F74A8DA843A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
